--- a/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
+++ b/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
@@ -3647,13 +3647,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE60"/>
-  <sheetFormatPr defaultRowHeight="14.5" ns3:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -3682,7 +3682,7 @@
     <col min="31" max="31" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="26.15" customHeight="1" ns3:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="176" t="s">
         <v>41</v>
       </c>
@@ -3717,7 +3717,7 @@
       <c r="AD1" s="138"/>
       <c r="AE1" s="138"/>
     </row>
-    <row r="2" spans="1:31" ns3:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" s="169" t="s">
         <v>42</v>
       </c>
@@ -3752,7 +3752,7 @@
       <c r="AD2" s="138"/>
       <c r="AE2" s="138"/>
     </row>
-    <row r="4" spans="1:31" ht="19" customHeight="1" ns3:dyDescent="0.35">
+    <row r="4" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="152" t="s">
         <v>43</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="AD4" s="147"/>
       <c r="AE4" s="148"/>
     </row>
-    <row r="5" spans="1:31" ns3:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="159" t="s">
         <v>44</v>
       </c>
@@ -3832,7 +3832,7 @@
       <c r="AD5" s="147"/>
       <c r="AE5" s="148"/>
     </row>
-    <row r="6" spans="1:31" ht="22" customHeight="1" ns3:dyDescent="0.35">
+    <row r="6" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="177">
         <f>$K$13</f>
         <v>0</v>
@@ -3883,7 +3883,7 @@
       <c r="AD6" s="154"/>
       <c r="AE6" s="155"/>
     </row>
-    <row r="7" spans="1:31" ht="14.15" customHeight="1" ns3:dyDescent="0.35">
+    <row r="7" spans="1:31" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="156"/>
       <c r="B7" s="157"/>
       <c r="C7" s="157"/>
@@ -3916,7 +3916,7 @@
       <c r="AD7" s="157"/>
       <c r="AE7" s="158"/>
     </row>
-    <row r="8" spans="1:31" ns3:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="74" t="s">
         <v>50</v>
       </c>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Y8" s="116"/>
     </row>
-    <row r="9" spans="1:31" ht="19" customHeight="1" ns3:dyDescent="0.35">
+    <row r="9" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="152" t="s">
         <v>55</v>
       </c>
@@ -3966,7 +3966,7 @@
       <c r="Z9" s="147"/>
       <c r="AA9" s="148"/>
     </row>
-    <row r="10" spans="1:31" ns3:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="146" t="s">
         <v>57</v>
       </c>
@@ -4005,7 +4005,7 @@
       <c r="Z10" s="147"/>
       <c r="AA10" s="148"/>
     </row>
-    <row r="11" spans="1:31" ns3:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="146" t="s">
         <v>62</v>
       </c>
@@ -4045,7 +4045,7 @@
       <c r="Z11" s="147"/>
       <c r="AA11" s="148"/>
     </row>
-    <row r="12" spans="1:31" ns3:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="146" t="s">
         <v>66</v>
       </c>
@@ -4081,7 +4081,7 @@
       <c r="Z12" s="154"/>
       <c r="AA12" s="155"/>
     </row>
-    <row r="13" spans="1:31" ns3:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="146" t="s">
         <v>70</v>
       </c>
@@ -4112,7 +4112,7 @@
       <c r="Z13" s="157"/>
       <c r="AA13" s="158"/>
     </row>
-    <row r="14" spans="1:31" ns3:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="146" t="s">
         <v>72</v>
       </c>
@@ -4130,7 +4130,7 @@
       <c r="L14" s="147"/>
       <c r="M14" s="148"/>
     </row>
-    <row r="15" spans="1:31" ht="19" customHeight="1" ns3:dyDescent="0.35">
+    <row r="15" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="146" t="s">
         <v>74</v>
       </c>
@@ -4163,7 +4163,7 @@
       <c r="Z15" s="147"/>
       <c r="AA15" s="148"/>
     </row>
-    <row r="16" spans="1:31" ns3:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="146" t="s">
         <v>77</v>
       </c>
@@ -4206,7 +4206,7 @@
       <c r="Z16" s="147"/>
       <c r="AA16" s="148"/>
     </row>
-    <row r="17" spans="1:31" ns3:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" s="146" t="s">
         <v>81</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="Z17" s="147"/>
       <c r="AA17" s="148"/>
     </row>
-    <row r="19" spans="1:31" ht="19" customHeight="1" ns3:dyDescent="0.35">
+    <row r="19" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="152" t="s">
         <v>85</v>
       </c>
@@ -4284,7 +4284,7 @@
       <c r="Z19" s="147"/>
       <c r="AA19" s="148"/>
     </row>
-    <row r="20" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="146" t="s">
         <v>87</v>
       </c>
@@ -4323,7 +4323,7 @@
       <c r="Z20" s="147"/>
       <c r="AA20" s="148"/>
     </row>
-    <row r="21" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="146" t="s">
         <v>92</v>
       </c>
@@ -4360,7 +4360,7 @@
       <c r="Z21" s="147"/>
       <c r="AA21" s="148"/>
     </row>
-    <row r="22" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="146" t="s">
         <v>96</v>
       </c>
@@ -4397,7 +4397,7 @@
       <c r="Z22" s="147"/>
       <c r="AA22" s="148"/>
     </row>
-    <row r="23" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="146" t="s">
         <v>99</v>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="Z23" s="147"/>
       <c r="AA23" s="148"/>
     </row>
-    <row r="24" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="146" t="s">
         <v>102</v>
       </c>
@@ -4473,7 +4473,7 @@
       <c r="Z24" s="147"/>
       <c r="AA24" s="148"/>
     </row>
-    <row r="25" spans="1:31" ht="15.75" customHeight="1" ns3:dyDescent="0.35">
+    <row r="25" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O25" s="146" t="s">
         <v>106</v>
       </c>
@@ -4492,7 +4492,7 @@
       <c r="Z25" s="147"/>
       <c r="AA25" s="148"/>
     </row>
-    <row r="27" spans="1:31" ht="19" customHeight="1" ns3:dyDescent="0.35">
+    <row r="27" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="152" t="s">
         <v>107</v>
       </c>
@@ -4527,7 +4527,7 @@
       <c r="AD27" s="147"/>
       <c r="AE27" s="148"/>
     </row>
-    <row r="28" spans="1:31" ht="15" customHeight="1" ns3:dyDescent="0.35">
+    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="151" t="s">
         <v>108</v>
       </c>
@@ -4578,7 +4578,7 @@
       <c r="AD28" s="147"/>
       <c r="AE28" s="148"/>
     </row>
-    <row r="29" spans="1:31" ht="34" customHeight="1" ns3:dyDescent="0.35">
+    <row r="29" spans="1:31" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>117</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ns3:dyDescent="0.35">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -4757,7 +4757,7 @@
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
     </row>
-    <row r="31" spans="1:31" ns3:dyDescent="0.35">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -4841,7 +4841,7 @@
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
     </row>
-    <row r="32" spans="1:31" ns3:dyDescent="0.35">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -4925,7 +4925,7 @@
       <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
     </row>
-    <row r="33" spans="1:31" ns3:dyDescent="0.35">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -5009,7 +5009,7 @@
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
     </row>
-    <row r="34" spans="1:31" ns3:dyDescent="0.35">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -5093,7 +5093,7 @@
       <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
     </row>
-    <row r="35" spans="1:31" ns3:dyDescent="0.35">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -5177,7 +5177,7 @@
       <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
     </row>
-    <row r="36" spans="1:31" ns3:dyDescent="0.35">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -5261,7 +5261,7 @@
       <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
     </row>
-    <row r="37" spans="1:31" ns3:dyDescent="0.35">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -5345,7 +5345,7 @@
       <c r="AD37" s="5"/>
       <c r="AE37" s="5"/>
     </row>
-    <row r="38" spans="1:31" ns3:dyDescent="0.35">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -5429,7 +5429,7 @@
       <c r="AD38" s="5"/>
       <c r="AE38" s="5"/>
     </row>
-    <row r="39" spans="1:31" ns3:dyDescent="0.35">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -5513,7 +5513,7 @@
       <c r="AD39" s="5"/>
       <c r="AE39" s="5"/>
     </row>
-    <row r="40" spans="1:31" ns3:dyDescent="0.35">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -5597,7 +5597,7 @@
       <c r="AD40" s="5"/>
       <c r="AE40" s="5"/>
     </row>
-    <row r="41" spans="1:31" ns3:dyDescent="0.35">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -5681,7 +5681,7 @@
       <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
     </row>
-    <row r="42" spans="1:31" ns3:dyDescent="0.35">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -5765,7 +5765,7 @@
       <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
     </row>
-    <row r="43" spans="1:31" ns3:dyDescent="0.35">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -5849,7 +5849,7 @@
       <c r="AD43" s="5"/>
       <c r="AE43" s="5"/>
     </row>
-    <row r="44" spans="1:31" ns3:dyDescent="0.35">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -5933,7 +5933,7 @@
       <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
     </row>
-    <row r="45" spans="1:31" ns3:dyDescent="0.35">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -6017,7 +6017,7 @@
       <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
     </row>
-    <row r="46" spans="1:31" ns3:dyDescent="0.35">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -6101,7 +6101,7 @@
       <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
     </row>
-    <row r="47" spans="1:31" ns3:dyDescent="0.35">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -6185,7 +6185,7 @@
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
     </row>
-    <row r="48" spans="1:31" ns3:dyDescent="0.35">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6269,7 +6269,7 @@
       <c r="AD48" s="5"/>
       <c r="AE48" s="5"/>
     </row>
-    <row r="49" spans="1:31" ns3:dyDescent="0.35">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -6353,7 +6353,7 @@
       <c r="AD49" s="5"/>
       <c r="AE49" s="5"/>
     </row>
-    <row r="50" spans="1:31" ns3:dyDescent="0.35">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -6437,7 +6437,7 @@
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
     </row>
-    <row r="51" spans="1:31" ns3:dyDescent="0.35">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -6521,7 +6521,7 @@
       <c r="AD51" s="5"/>
       <c r="AE51" s="5"/>
     </row>
-    <row r="52" spans="1:31" ns3:dyDescent="0.35">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -6605,7 +6605,7 @@
       <c r="AD52" s="5"/>
       <c r="AE52" s="5"/>
     </row>
-    <row r="53" spans="1:31" ns3:dyDescent="0.35">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -6689,7 +6689,7 @@
       <c r="AD53" s="5"/>
       <c r="AE53" s="5"/>
     </row>
-    <row r="54" spans="1:31" ns3:dyDescent="0.35">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -6773,7 +6773,7 @@
       <c r="AD54" s="5"/>
       <c r="AE54" s="5"/>
     </row>
-    <row r="55" spans="1:31" ns3:dyDescent="0.35">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -6857,7 +6857,7 @@
       <c r="AD55" s="5"/>
       <c r="AE55" s="5"/>
     </row>
-    <row r="56" spans="1:31" ns3:dyDescent="0.35">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -6941,7 +6941,7 @@
       <c r="AD56" s="5"/>
       <c r="AE56" s="5"/>
     </row>
-    <row r="57" spans="1:31" ns3:dyDescent="0.35">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -7025,7 +7025,7 @@
       <c r="AD57" s="5"/>
       <c r="AE57" s="5"/>
     </row>
-    <row r="58" spans="1:31" ns3:dyDescent="0.35">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -7109,7 +7109,7 @@
       <c r="AD58" s="5"/>
       <c r="AE58" s="5"/>
     </row>
-    <row r="59" spans="1:31" ns3:dyDescent="0.35">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -7193,7 +7193,7 @@
       <c r="AD59" s="5"/>
       <c r="AE59" s="5"/>
     </row>
-    <row r="60" spans="1:31" ns3:dyDescent="0.35">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>37</v>
       </c>
@@ -7402,16 +7402,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="D20" ns2:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"FIJO,VARIABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B30:B59 D21 R10" ns2:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B30:B59 D21 R10" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" ns2:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Y20:Y25" ns2:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Y20:Y25" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"✓,✗"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
+++ b/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
@@ -26,7 +26,7 @@
     <sheet name="CI Variable" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="CI Variable +3%" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
+++ b/public/plantilla/Calculo_Deuda_y_Subasta.xlsx
@@ -2271,72 +2271,60 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="27" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="28" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="17" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="27" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2344,16 +2332,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="17" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2362,43 +2347,22 @@
     <xf numFmtId="167" fontId="18" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2407,11 +2371,14 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="44" fontId="22" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2432,6 +2399,39 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="27" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3683,232 +3683,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="138"/>
-      <c r="T1" s="138"/>
-      <c r="U1" s="138"/>
-      <c r="V1" s="138"/>
-      <c r="W1" s="138"/>
-      <c r="X1" s="138"/>
-      <c r="Y1" s="138"/>
-      <c r="Z1" s="138"/>
-      <c r="AA1" s="138"/>
-      <c r="AB1" s="138"/>
-      <c r="AC1" s="138"/>
-      <c r="AD1" s="138"/>
-      <c r="AE1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="131"/>
+      <c r="AA1" s="131"/>
+      <c r="AB1" s="131"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="131"/>
+      <c r="AE1" s="131"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="138"/>
-      <c r="T2" s="138"/>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="138"/>
-      <c r="Z2" s="138"/>
-      <c r="AA2" s="138"/>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="131"/>
+      <c r="V2" s="131"/>
+      <c r="W2" s="131"/>
+      <c r="X2" s="131"/>
+      <c r="Y2" s="131"/>
+      <c r="Z2" s="131"/>
+      <c r="AA2" s="131"/>
+      <c r="AB2" s="131"/>
+      <c r="AC2" s="131"/>
+      <c r="AD2" s="131"/>
+      <c r="AE2" s="131"/>
     </row>
     <row r="4" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="147"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="147"/>
-      <c r="R4" s="147"/>
-      <c r="S4" s="147"/>
-      <c r="T4" s="147"/>
-      <c r="U4" s="147"/>
-      <c r="V4" s="147"/>
-      <c r="W4" s="147"/>
-      <c r="X4" s="147"/>
-      <c r="Y4" s="147"/>
-      <c r="Z4" s="147"/>
-      <c r="AA4" s="147"/>
-      <c r="AB4" s="147"/>
-      <c r="AC4" s="147"/>
-      <c r="AD4" s="147"/>
-      <c r="AE4" s="148"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="139"/>
+      <c r="Q4" s="139"/>
+      <c r="R4" s="139"/>
+      <c r="S4" s="139"/>
+      <c r="T4" s="139"/>
+      <c r="U4" s="139"/>
+      <c r="V4" s="139"/>
+      <c r="W4" s="139"/>
+      <c r="X4" s="139"/>
+      <c r="Y4" s="139"/>
+      <c r="Z4" s="139"/>
+      <c r="AA4" s="139"/>
+      <c r="AB4" s="139"/>
+      <c r="AC4" s="139"/>
+      <c r="AD4" s="139"/>
+      <c r="AE4" s="140"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="159" t="s">
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="159" t="s">
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="159" t="s">
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="147"/>
-      <c r="S5" s="147"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="180" t="s">
+      <c r="Q5" s="139"/>
+      <c r="R5" s="139"/>
+      <c r="S5" s="139"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="163" t="s">
         <v>48</v>
       </c>
-      <c r="V5" s="147"/>
-      <c r="W5" s="147"/>
-      <c r="X5" s="147"/>
-      <c r="Y5" s="148"/>
-      <c r="Z5" s="159" t="s">
+      <c r="V5" s="139"/>
+      <c r="W5" s="139"/>
+      <c r="X5" s="139"/>
+      <c r="Y5" s="140"/>
+      <c r="Z5" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="147"/>
-      <c r="AB5" s="147"/>
-      <c r="AC5" s="147"/>
-      <c r="AD5" s="147"/>
-      <c r="AE5" s="148"/>
+      <c r="AA5" s="139"/>
+      <c r="AB5" s="139"/>
+      <c r="AC5" s="139"/>
+      <c r="AD5" s="139"/>
+      <c r="AE5" s="140"/>
     </row>
     <row r="6" spans="1:31" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="177">
+      <c r="A6" s="132">
         <f>$K$13</f>
       </c>
-      <c r="B6" s="154"/>
-      <c r="C6" s="154"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="155"/>
-      <c r="F6" s="161">
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="165">
         <f>$K$11</f>
       </c>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="155"/>
-      <c r="K6" s="177">
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="132">
         <f>$K$16</f>
       </c>
-      <c r="L6" s="154"/>
-      <c r="M6" s="154"/>
-      <c r="N6" s="154"/>
-      <c r="O6" s="155"/>
-      <c r="P6" s="165">
+      <c r="L6" s="133"/>
+      <c r="M6" s="133"/>
+      <c r="N6" s="133"/>
+      <c r="O6" s="134"/>
+      <c r="P6" s="158">
         <f>V60</f>
       </c>
-      <c r="Q6" s="154"/>
-      <c r="R6" s="154"/>
-      <c r="S6" s="154"/>
-      <c r="T6" s="155"/>
-      <c r="U6" s="174">
+      <c r="Q6" s="133"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="133"/>
+      <c r="T6" s="134"/>
+      <c r="U6" s="150">
         <f>W60</f>
       </c>
-      <c r="V6" s="154"/>
-      <c r="W6" s="154"/>
-      <c r="X6" s="154"/>
-      <c r="Y6" s="155"/>
-      <c r="Z6" s="170">
+      <c r="V6" s="133"/>
+      <c r="W6" s="133"/>
+      <c r="X6" s="133"/>
+      <c r="Y6" s="134"/>
+      <c r="Z6" s="161">
         <f>IFERROR(V60/$K$16,0)</f>
       </c>
-      <c r="AA6" s="154"/>
-      <c r="AB6" s="154"/>
-      <c r="AC6" s="154"/>
-      <c r="AD6" s="154"/>
-      <c r="AE6" s="155"/>
+      <c r="AA6" s="133"/>
+      <c r="AB6" s="133"/>
+      <c r="AC6" s="133"/>
+      <c r="AD6" s="133"/>
+      <c r="AE6" s="134"/>
     </row>
     <row r="7" spans="1:31" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="158"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="156"/>
-      <c r="L7" s="157"/>
-      <c r="M7" s="157"/>
-      <c r="N7" s="157"/>
-      <c r="O7" s="158"/>
-      <c r="P7" s="156"/>
-      <c r="Q7" s="157"/>
-      <c r="R7" s="157"/>
-      <c r="S7" s="157"/>
-      <c r="T7" s="158"/>
-      <c r="U7" s="156"/>
-      <c r="V7" s="157"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="157"/>
-      <c r="Y7" s="158"/>
-      <c r="Z7" s="156"/>
-      <c r="AA7" s="157"/>
-      <c r="AB7" s="157"/>
-      <c r="AC7" s="157"/>
-      <c r="AD7" s="157"/>
-      <c r="AE7" s="158"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="136"/>
+      <c r="N7" s="136"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="136"/>
+      <c r="R7" s="136"/>
+      <c r="S7" s="136"/>
+      <c r="T7" s="137"/>
+      <c r="U7" s="135"/>
+      <c r="V7" s="136"/>
+      <c r="W7" s="136"/>
+      <c r="X7" s="136"/>
+      <c r="Y7" s="137"/>
+      <c r="Z7" s="135"/>
+      <c r="AA7" s="136"/>
+      <c r="AB7" s="136"/>
+      <c r="AC7" s="136"/>
+      <c r="AD7" s="136"/>
+      <c r="AE7" s="137"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="74" t="s">
@@ -3932,633 +3932,633 @@
       <c r="A9" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="147"/>
-      <c r="H9" s="147"/>
-      <c r="I9" s="147"/>
-      <c r="J9" s="147"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="148"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="140"/>
       <c r="O9" s="152" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="147"/>
-      <c r="S9" s="147"/>
-      <c r="T9" s="147"/>
-      <c r="U9" s="147"/>
-      <c r="V9" s="147"/>
-      <c r="W9" s="147"/>
-      <c r="X9" s="147"/>
-      <c r="Y9" s="147"/>
-      <c r="Z9" s="147"/>
-      <c r="AA9" s="148"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="140"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="147"/>
-      <c r="F10" s="148"/>
-      <c r="H10" s="146" t="s">
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="140"/>
+      <c r="H10" s="143" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="147"/>
-      <c r="J10" s="148"/>
-      <c r="K10" s="149">
+      <c r="I10" s="139"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="162">
         <f>SUM($D$10:$D$13)</f>
       </c>
-      <c r="L10" s="147"/>
-      <c r="M10" s="148"/>
-      <c r="O10" s="146" t="s">
+      <c r="L10" s="139"/>
+      <c r="M10" s="140"/>
+      <c r="O10" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="147"/>
-      <c r="Q10" s="148"/>
-      <c r="R10" s="178" t="s">
+      <c r="P10" s="139"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="S10" s="147"/>
-      <c r="T10" s="148"/>
-      <c r="V10" s="146" t="s">
+      <c r="S10" s="139"/>
+      <c r="T10" s="140"/>
+      <c r="V10" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="W10" s="147"/>
-      <c r="X10" s="148"/>
-      <c r="Y10" s="150"/>
-      <c r="Z10" s="147"/>
-      <c r="AA10" s="148"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="140"/>
+      <c r="Y10" s="141"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="140"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="H11" s="146" t="s">
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="140"/>
+      <c r="H11" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="167">
+      <c r="I11" s="139"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="159">
         <f>'Cálculo Intereses'!$D$21</f>
       </c>
-      <c r="L11" s="147"/>
-      <c r="M11" s="148"/>
-      <c r="O11" s="146" t="s">
+      <c r="L11" s="139"/>
+      <c r="M11" s="140"/>
+      <c r="O11" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="148"/>
-      <c r="R11" s="150"/>
-      <c r="S11" s="147"/>
-      <c r="T11" s="148"/>
-      <c r="V11" s="146" t="s">
+      <c r="P11" s="139"/>
+      <c r="Q11" s="140"/>
+      <c r="R11" s="141"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="140"/>
+      <c r="V11" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="W11" s="147"/>
-      <c r="X11" s="148"/>
-      <c r="Y11" s="149">
+      <c r="W11" s="139"/>
+      <c r="X11" s="140"/>
+      <c r="Y11" s="162">
         <f>IF($Y$10+$R$11=0,$K$10,$Y$10+$R$11)</f>
       </c>
-      <c r="Z11" s="147"/>
-      <c r="AA11" s="148"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="140"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="143" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="148"/>
-      <c r="H12" s="146" t="s">
+      <c r="B12" s="139"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="141"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="140"/>
+      <c r="H12" s="143" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="147"/>
-      <c r="J12" s="148"/>
-      <c r="K12" s="149">
+      <c r="I12" s="139"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="162">
         <f>IF($D$17=0,$D$14,MIN(($K$10*0.05),IF($D$14&gt;0,$D$14,$K$10*0.05)))</f>
       </c>
-      <c r="L12" s="147"/>
-      <c r="M12" s="148"/>
-      <c r="O12" s="146" t="s">
+      <c r="L12" s="139"/>
+      <c r="M12" s="140"/>
+      <c r="O12" s="143" t="s">
         <v>68</v>
       </c>
-      <c r="P12" s="147"/>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="153"/>
-      <c r="S12" s="154"/>
-      <c r="T12" s="154"/>
-      <c r="U12" s="154"/>
-      <c r="V12" s="154"/>
-      <c r="W12" s="154"/>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="154"/>
-      <c r="Z12" s="154"/>
-      <c r="AA12" s="155"/>
+      <c r="P12" s="139"/>
+      <c r="Q12" s="140"/>
+      <c r="R12" s="164"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="134"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="148"/>
-      <c r="H13" s="146" t="s">
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="140"/>
+      <c r="H13" s="143" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="147"/>
-      <c r="J13" s="148"/>
-      <c r="K13" s="162">
+      <c r="I13" s="139"/>
+      <c r="J13" s="140"/>
+      <c r="K13" s="154">
         <f>$K$10+$K$11+IF($D$17&gt;0,$K$12,$D$14)</f>
       </c>
-      <c r="L13" s="163"/>
-      <c r="M13" s="164"/>
-      <c r="R13" s="156"/>
-      <c r="S13" s="157"/>
-      <c r="T13" s="157"/>
-      <c r="U13" s="157"/>
-      <c r="V13" s="157"/>
-      <c r="W13" s="157"/>
-      <c r="X13" s="157"/>
-      <c r="Y13" s="157"/>
-      <c r="Z13" s="157"/>
-      <c r="AA13" s="158"/>
+      <c r="L13" s="155"/>
+      <c r="M13" s="156"/>
+      <c r="R13" s="135"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="V13" s="136"/>
+      <c r="W13" s="136"/>
+      <c r="X13" s="136"/>
+      <c r="Y13" s="136"/>
+      <c r="Z13" s="136"/>
+      <c r="AA13" s="137"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="143" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="148"/>
-      <c r="H14" s="146" t="s">
+      <c r="B14" s="139"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="140"/>
+      <c r="H14" s="143" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="147"/>
-      <c r="J14" s="148"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="148"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="141"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="140"/>
     </row>
     <row r="15" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="172"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="148"/>
-      <c r="H15" s="146" t="s">
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="140"/>
+      <c r="H15" s="143" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="147"/>
-      <c r="J15" s="148"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="148"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="140"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="140"/>
       <c r="O15" s="152" t="s">
         <v>76</v>
       </c>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="147"/>
-      <c r="R15" s="147"/>
-      <c r="S15" s="147"/>
-      <c r="T15" s="147"/>
-      <c r="U15" s="147"/>
-      <c r="V15" s="147"/>
-      <c r="W15" s="147"/>
-      <c r="X15" s="147"/>
-      <c r="Y15" s="147"/>
-      <c r="Z15" s="147"/>
-      <c r="AA15" s="148"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="140"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="172"/>
-      <c r="E16" s="147"/>
-      <c r="F16" s="148"/>
-      <c r="H16" s="146" t="s">
+      <c r="B16" s="139"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="140"/>
+      <c r="H16" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="147"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="162">
+      <c r="I16" s="139"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="154">
         <f>$K$13+$K$14+$K$15</f>
       </c>
-      <c r="L16" s="163"/>
-      <c r="M16" s="164"/>
-      <c r="O16" s="146" t="s">
+      <c r="L16" s="155"/>
+      <c r="M16" s="156"/>
+      <c r="O16" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="148"/>
-      <c r="R16" s="171">
+      <c r="P16" s="139"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="157">
         <f>IF(AND(ISNUMBER($D$16),ISNUMBER($D$15)),$D$16-$D$15,0)</f>
       </c>
-      <c r="S16" s="147"/>
-      <c r="T16" s="148"/>
-      <c r="V16" s="146" t="s">
+      <c r="S16" s="139"/>
+      <c r="T16" s="140"/>
+      <c r="V16" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="W16" s="147"/>
-      <c r="X16" s="148"/>
-      <c r="Y16" s="175">
+      <c r="W16" s="139"/>
+      <c r="X16" s="140"/>
+      <c r="Y16" s="148">
         <f>'Cálculo Intereses'!$D$23</f>
       </c>
-      <c r="Z16" s="147"/>
-      <c r="AA16" s="148"/>
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="140"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A17" s="146" t="s">
+      <c r="A17" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="171">
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="157">
         <f>COUNTIF(B30:B59,"Y")</f>
       </c>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="H17" s="146" t="s">
+      <c r="E17" s="139"/>
+      <c r="F17" s="140"/>
+      <c r="H17" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="147"/>
-      <c r="J17" s="148"/>
-      <c r="K17" s="149">
+      <c r="I17" s="139"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="162">
         <f>W30</f>
       </c>
-      <c r="L17" s="147"/>
-      <c r="M17" s="148"/>
-      <c r="O17" s="146" t="s">
+      <c r="L17" s="139"/>
+      <c r="M17" s="140"/>
+      <c r="O17" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="P17" s="147"/>
-      <c r="Q17" s="148"/>
-      <c r="R17" s="173">
+      <c r="P17" s="139"/>
+      <c r="Q17" s="140"/>
+      <c r="R17" s="153">
         <f>'Cálculo Intereses'!$D$24</f>
       </c>
-      <c r="S17" s="147"/>
-      <c r="T17" s="148"/>
-      <c r="V17" s="146" t="s">
+      <c r="S17" s="139"/>
+      <c r="T17" s="140"/>
+      <c r="V17" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="W17" s="147"/>
-      <c r="X17" s="148"/>
-      <c r="Y17" s="175" t="str">
+      <c r="W17" s="139"/>
+      <c r="X17" s="140"/>
+      <c r="Y17" s="148" t="str">
         <f>'Cálculo Intereses'!$D$18</f>
       </c>
-      <c r="Z17" s="147"/>
-      <c r="AA17" s="148"/>
+      <c r="Z17" s="139"/>
+      <c r="AA17" s="140"/>
     </row>
     <row r="19" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="152" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="147"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="147"/>
-      <c r="G19" s="147"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="147"/>
-      <c r="J19" s="147"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="148"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139"/>
+      <c r="M19" s="140"/>
       <c r="O19" s="152" t="s">
         <v>86</v>
       </c>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="147"/>
-      <c r="W19" s="147"/>
-      <c r="X19" s="147"/>
-      <c r="Y19" s="147"/>
-      <c r="Z19" s="147"/>
-      <c r="AA19" s="148"/>
+      <c r="P19" s="139"/>
+      <c r="Q19" s="139"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139"/>
+      <c r="T19" s="139"/>
+      <c r="U19" s="139"/>
+      <c r="V19" s="139"/>
+      <c r="W19" s="139"/>
+      <c r="X19" s="139"/>
+      <c r="Y19" s="139"/>
+      <c r="Z19" s="139"/>
+      <c r="AA19" s="140"/>
     </row>
     <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="146" t="s">
+      <c r="A20" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="148"/>
-      <c r="D20" s="178" t="s">
+      <c r="B20" s="139"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="138" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="147"/>
-      <c r="F20" s="148"/>
-      <c r="H20" s="146" t="s">
+      <c r="E20" s="139"/>
+      <c r="F20" s="140"/>
+      <c r="H20" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="147"/>
-      <c r="J20" s="148"/>
-      <c r="K20" s="166" t="s">
+      <c r="I20" s="139"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="142" t="s">
         <v>89</v>
       </c>
-      <c r="L20" s="147"/>
-      <c r="M20" s="148"/>
-      <c r="O20" s="146" t="s">
+      <c r="L20" s="139"/>
+      <c r="M20" s="140"/>
+      <c r="O20" s="143" t="s">
         <v>90</v>
       </c>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="147"/>
-      <c r="R20" s="147"/>
-      <c r="S20" s="147"/>
-      <c r="T20" s="147"/>
-      <c r="U20" s="147"/>
-      <c r="V20" s="147"/>
-      <c r="W20" s="147"/>
-      <c r="X20" s="148"/>
-      <c r="Y20" s="168" t="s">
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
+      <c r="T20" s="139"/>
+      <c r="U20" s="139"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="139"/>
+      <c r="X20" s="140"/>
+      <c r="Y20" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z20" s="147"/>
-      <c r="AA20" s="148"/>
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="140"/>
     </row>
     <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="143" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="166" t="s">
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="147"/>
-      <c r="F21" s="148"/>
-      <c r="H21" s="146" t="s">
+      <c r="E21" s="139"/>
+      <c r="F21" s="140"/>
+      <c r="H21" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="147"/>
-      <c r="J21" s="148"/>
-      <c r="K21" s="179"/>
-      <c r="L21" s="147"/>
-      <c r="M21" s="148"/>
-      <c r="O21" s="146" t="s">
+      <c r="I21" s="139"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="145"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="140"/>
+      <c r="O21" s="143" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="147"/>
-      <c r="R21" s="147"/>
-      <c r="S21" s="147"/>
-      <c r="T21" s="147"/>
-      <c r="U21" s="147"/>
-      <c r="V21" s="147"/>
-      <c r="W21" s="147"/>
-      <c r="X21" s="148"/>
-      <c r="Y21" s="168" t="s">
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="140"/>
+      <c r="Y21" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z21" s="147"/>
-      <c r="AA21" s="148"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="140"/>
     </row>
     <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="146" t="s">
+      <c r="A22" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="147"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="148"/>
-      <c r="H22" s="146" t="s">
+      <c r="B22" s="139"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="140"/>
+      <c r="H22" s="143" t="s">
         <v>97</v>
       </c>
-      <c r="I22" s="147"/>
-      <c r="J22" s="148"/>
-      <c r="K22" s="166">
+      <c r="I22" s="139"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="142">
         <v>12</v>
       </c>
-      <c r="L22" s="147"/>
-      <c r="M22" s="148"/>
-      <c r="O22" s="146" t="s">
+      <c r="L22" s="139"/>
+      <c r="M22" s="140"/>
+      <c r="O22" s="143" t="s">
         <v>98</v>
       </c>
-      <c r="P22" s="147"/>
-      <c r="Q22" s="147"/>
-      <c r="R22" s="147"/>
-      <c r="S22" s="147"/>
-      <c r="T22" s="147"/>
-      <c r="U22" s="147"/>
-      <c r="V22" s="147"/>
-      <c r="W22" s="147"/>
-      <c r="X22" s="148"/>
-      <c r="Y22" s="168" t="s">
+      <c r="P22" s="139"/>
+      <c r="Q22" s="139"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="139"/>
+      <c r="T22" s="139"/>
+      <c r="U22" s="139"/>
+      <c r="V22" s="139"/>
+      <c r="W22" s="139"/>
+      <c r="X22" s="140"/>
+      <c r="Y22" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z22" s="147"/>
-      <c r="AA22" s="148"/>
+      <c r="Z22" s="139"/>
+      <c r="AA22" s="140"/>
     </row>
     <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="143" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="160"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="H23" s="146" t="s">
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="140"/>
+      <c r="H23" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="I23" s="147"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="172">
+      <c r="I23" s="139"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="149">
         <v>43814</v>
       </c>
-      <c r="L23" s="147"/>
-      <c r="M23" s="148"/>
-      <c r="O23" s="146" t="s">
+      <c r="L23" s="139"/>
+      <c r="M23" s="140"/>
+      <c r="O23" s="143" t="s">
         <v>101</v>
       </c>
-      <c r="P23" s="147"/>
-      <c r="Q23" s="147"/>
-      <c r="R23" s="147"/>
-      <c r="S23" s="147"/>
-      <c r="T23" s="147"/>
-      <c r="U23" s="147"/>
-      <c r="V23" s="147"/>
-      <c r="W23" s="147"/>
-      <c r="X23" s="148"/>
-      <c r="Y23" s="168" t="s">
+      <c r="P23" s="139"/>
+      <c r="Q23" s="139"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139"/>
+      <c r="T23" s="139"/>
+      <c r="U23" s="139"/>
+      <c r="V23" s="139"/>
+      <c r="W23" s="139"/>
+      <c r="X23" s="140"/>
+      <c r="Y23" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z23" s="147"/>
-      <c r="AA23" s="148"/>
+      <c r="Z23" s="139"/>
+      <c r="AA23" s="140"/>
     </row>
     <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="166" t="s">
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="147"/>
-      <c r="F24" s="148"/>
-      <c r="H24" s="146" t="s">
+      <c r="E24" s="139"/>
+      <c r="F24" s="140"/>
+      <c r="H24" s="143" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="147"/>
-      <c r="J24" s="148"/>
-      <c r="K24" s="166">
+      <c r="I24" s="139"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="142">
         <v>1</v>
       </c>
-      <c r="L24" s="147"/>
-      <c r="M24" s="148"/>
-      <c r="O24" s="146" t="s">
+      <c r="L24" s="139"/>
+      <c r="M24" s="140"/>
+      <c r="O24" s="143" t="s">
         <v>105</v>
       </c>
-      <c r="P24" s="147"/>
-      <c r="Q24" s="147"/>
-      <c r="R24" s="147"/>
-      <c r="S24" s="147"/>
-      <c r="T24" s="147"/>
-      <c r="U24" s="147"/>
-      <c r="V24" s="147"/>
-      <c r="W24" s="147"/>
-      <c r="X24" s="148"/>
-      <c r="Y24" s="168" t="s">
+      <c r="P24" s="139"/>
+      <c r="Q24" s="139"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139"/>
+      <c r="W24" s="139"/>
+      <c r="X24" s="140"/>
+      <c r="Y24" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z24" s="147"/>
-      <c r="AA24" s="148"/>
+      <c r="Z24" s="139"/>
+      <c r="AA24" s="140"/>
     </row>
     <row r="25" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="O25" s="146" t="s">
+      <c r="O25" s="143" t="s">
         <v>106</v>
       </c>
-      <c r="P25" s="147"/>
-      <c r="Q25" s="147"/>
-      <c r="R25" s="147"/>
-      <c r="S25" s="147"/>
-      <c r="T25" s="147"/>
-      <c r="U25" s="147"/>
-      <c r="V25" s="147"/>
-      <c r="W25" s="147"/>
-      <c r="X25" s="148"/>
-      <c r="Y25" s="168" t="s">
+      <c r="P25" s="139"/>
+      <c r="Q25" s="139"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="139"/>
+      <c r="T25" s="139"/>
+      <c r="U25" s="139"/>
+      <c r="V25" s="139"/>
+      <c r="W25" s="139"/>
+      <c r="X25" s="140"/>
+      <c r="Y25" s="147" t="s">
         <v>91</v>
       </c>
-      <c r="Z25" s="147"/>
-      <c r="AA25" s="148"/>
+      <c r="Z25" s="139"/>
+      <c r="AA25" s="140"/>
     </row>
     <row r="27" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="152" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="147"/>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="147"/>
-      <c r="J27" s="147"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="147"/>
-      <c r="O27" s="147"/>
-      <c r="P27" s="147"/>
-      <c r="Q27" s="147"/>
-      <c r="R27" s="147"/>
-      <c r="S27" s="147"/>
-      <c r="T27" s="147"/>
-      <c r="U27" s="147"/>
-      <c r="V27" s="147"/>
-      <c r="W27" s="147"/>
-      <c r="X27" s="147"/>
-      <c r="Y27" s="147"/>
-      <c r="Z27" s="147"/>
-      <c r="AA27" s="147"/>
-      <c r="AB27" s="147"/>
-      <c r="AC27" s="147"/>
-      <c r="AD27" s="147"/>
-      <c r="AE27" s="148"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="139"/>
+      <c r="N27" s="139"/>
+      <c r="O27" s="139"/>
+      <c r="P27" s="139"/>
+      <c r="Q27" s="139"/>
+      <c r="R27" s="139"/>
+      <c r="S27" s="139"/>
+      <c r="T27" s="139"/>
+      <c r="U27" s="139"/>
+      <c r="V27" s="139"/>
+      <c r="W27" s="139"/>
+      <c r="X27" s="139"/>
+      <c r="Y27" s="139"/>
+      <c r="Z27" s="139"/>
+      <c r="AA27" s="139"/>
+      <c r="AB27" s="139"/>
+      <c r="AC27" s="139"/>
+      <c r="AD27" s="139"/>
+      <c r="AE27" s="140"/>
     </row>
     <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="151" t="s">
+      <c r="A28" s="146" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="147"/>
-      <c r="C28" s="147"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="151" t="s">
+      <c r="B28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="146" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="147"/>
-      <c r="G28" s="147"/>
-      <c r="H28" s="148"/>
-      <c r="I28" s="151" t="s">
+      <c r="F28" s="139"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="J28" s="147"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="147"/>
-      <c r="M28" s="148"/>
-      <c r="N28" s="151" t="s">
+      <c r="J28" s="139"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="140"/>
+      <c r="N28" s="146" t="s">
         <v>111</v>
       </c>
-      <c r="O28" s="151" t="s">
+      <c r="O28" s="146" t="s">
         <v>112</v>
       </c>
-      <c r="P28" s="147"/>
-      <c r="Q28" s="147"/>
-      <c r="R28" s="147"/>
-      <c r="S28" s="148"/>
-      <c r="T28" s="151" t="s">
+      <c r="P28" s="139"/>
+      <c r="Q28" s="139"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="140"/>
+      <c r="T28" s="146" t="s">
         <v>113</v>
       </c>
-      <c r="U28" s="148"/>
-      <c r="V28" s="151" t="s">
+      <c r="U28" s="140"/>
+      <c r="V28" s="146" t="s">
         <v>114</v>
       </c>
-      <c r="W28" s="148"/>
-      <c r="X28" s="151" t="s">
+      <c r="W28" s="140"/>
+      <c r="X28" s="146" t="s">
         <v>115</v>
       </c>
-      <c r="Y28" s="148"/>
-      <c r="Z28" s="151" t="s">
+      <c r="Y28" s="140"/>
+      <c r="Z28" s="146" t="s">
         <v>116</v>
       </c>
-      <c r="AA28" s="147"/>
-      <c r="AB28" s="147"/>
-      <c r="AC28" s="147"/>
-      <c r="AD28" s="147"/>
-      <c r="AE28" s="148"/>
+      <c r="AA28" s="139"/>
+      <c r="AB28" s="139"/>
+      <c r="AC28" s="139"/>
+      <c r="AD28" s="139"/>
+      <c r="AE28" s="140"/>
     </row>
     <row r="29" spans="1:31" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
@@ -6732,6 +6732,94 @@
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="A4:AE4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="R12:AA13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O15:AA15"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="Z28:AE28"/>
+    <mergeCell ref="F6:J7"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="P6:T7"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="A2:AE2"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="Z6:AE7"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="O9:AA9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="U5:Y5"/>
+    <mergeCell ref="A6:E7"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="O23:X23"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="O24:X24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="O25:X25"/>
+    <mergeCell ref="A27:AE27"/>
+    <mergeCell ref="Y25:AA25"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="O22:X22"/>
+    <mergeCell ref="O21:X21"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="N28"/>
+    <mergeCell ref="O28:S28"/>
+    <mergeCell ref="Y23:AA23"/>
+    <mergeCell ref="U6:Y7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="Y17:AA17"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="Z5:AE5"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O19:AA19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="K6:O7"/>
     <mergeCell ref="D20:F20"/>
@@ -6756,94 +6844,6 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="O20:X20"/>
     <mergeCell ref="E28:H28"/>
-    <mergeCell ref="Y23:AA23"/>
-    <mergeCell ref="U6:Y7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="Y17:AA17"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="Z5:AE5"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O19:AA19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="O23:X23"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="O24:X24"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="O25:X25"/>
-    <mergeCell ref="A27:AE27"/>
-    <mergeCell ref="Y25:AA25"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="O22:X22"/>
-    <mergeCell ref="O21:X21"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="N28"/>
-    <mergeCell ref="P6:T7"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="A2:AE2"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="Z6:AE7"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="Y22:AA22"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="O9:AA9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="U5:Y5"/>
-    <mergeCell ref="A6:E7"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="O28:S28"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="A4:AE4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="R12:AA13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O15:AA15"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="Z28:AE28"/>
-    <mergeCell ref="F6:J7"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O10:Q10"/>
   </mergeCells>
   <conditionalFormatting sqref="Z6">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -7078,53 +7078,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="168" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="170" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="4" spans="1:16" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="152" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="140"/>
       <c r="G4" s="4" t="s">
         <v>163</v>
       </c>
@@ -7157,15 +7157,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="167">
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="159">
         <f>'Informe Subasta'!$D$10</f>
       </c>
-      <c r="E5" s="148"/>
+      <c r="E5" s="140"/>
       <c r="G5" s="11">
         <f t="shared" ref="G5:G68" si="0">IF(H5="","",ROW()-4)</f>
       </c>
@@ -7198,15 +7198,15 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="143" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="147"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="182">
+      <c r="B6" s="139"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="166">
         <f>'Informe Subasta'!$D$15</f>
       </c>
-      <c r="E6" s="148"/>
+      <c r="E6" s="140"/>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7239,15 +7239,15 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="147"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="182">
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="166">
         <f>'Informe Subasta'!$D$16</f>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="140"/>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7280,15 +7280,15 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="147"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="175" t="str">
+      <c r="B8" s="139"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="148" t="str">
         <f>'Informe Subasta'!$D$20</f>
       </c>
-      <c r="E8" s="148"/>
+      <c r="E8" s="140"/>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7321,15 +7321,15 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="175" t="str">
+      <c r="B9" s="139"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="148" t="str">
         <f>'Informe Subasta'!$K$20</f>
       </c>
-      <c r="E9" s="148"/>
+      <c r="E9" s="140"/>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7362,15 +7362,15 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="173">
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="153">
         <f>'Informe Subasta'!$K$21</f>
       </c>
-      <c r="E10" s="148"/>
+      <c r="E10" s="140"/>
       <c r="G10" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7403,15 +7403,15 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="143" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="175">
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="148">
         <f>'Informe Subasta'!$K$22</f>
       </c>
-      <c r="E11" s="148"/>
+      <c r="E11" s="140"/>
       <c r="G11" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7444,15 +7444,15 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="182">
+      <c r="B12" s="139"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="166">
         <f>'Informe Subasta'!$K$23</f>
       </c>
-      <c r="E12" s="148"/>
+      <c r="E12" s="140"/>
       <c r="G12" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7485,15 +7485,15 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="143" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="175">
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="148">
         <f>'Informe Subasta'!$K$24</f>
       </c>
-      <c r="E13" s="148"/>
+      <c r="E13" s="140"/>
       <c r="G13" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7526,15 +7526,15 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="175" t="str">
+      <c r="B14" s="139"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="148" t="str">
         <f>'Informe Subasta'!$D$24</f>
       </c>
-      <c r="E14" s="148"/>
+      <c r="E14" s="140"/>
       <c r="G14" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7567,15 +7567,15 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="143" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="175" t="str">
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="148" t="str">
         <f>'Informe Subasta'!$D$21</f>
       </c>
-      <c r="E15" s="148"/>
+      <c r="E15" s="140"/>
       <c r="G15" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7608,15 +7608,15 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="183">
+      <c r="B16" s="139"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="171">
         <f>'Informe Subasta'!$D$22</f>
       </c>
-      <c r="E16" s="148"/>
+      <c r="E16" s="140"/>
       <c r="G16" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7649,15 +7649,15 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="146" t="s">
+      <c r="A17" s="143" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="183">
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="171">
         <f>'Informe Subasta'!$D$23</f>
       </c>
-      <c r="E17" s="148"/>
+      <c r="E17" s="140"/>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7690,15 +7690,15 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="146" t="s">
+      <c r="A18" s="143" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="185" t="str">
+      <c r="B18" s="139"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="169" t="str">
         <f>IF(OR(ISNUMBER(SEARCH("legal",$D$9)),ISNUMBER(SEARCH("demora",$D$9)),ISNUMBER(SEARCH("mora procesal",$D$9)),ISNUMBER(SEARCH("576",$D$9))),"LEGAL","VARIABLE")</f>
       </c>
-      <c r="E18" s="148"/>
+      <c r="E18" s="140"/>
       <c r="G18" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7766,10 +7766,10 @@
       <c r="A20" s="152" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="148"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="140"/>
       <c r="G20" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7802,15 +7802,15 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="143" t="s">
         <v>177</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="181">
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="172">
         <f>IF($D$8="FIJO",($D$7-$D$6)*IF($D$15="Y",$D$16,$D$17)*$D$5/365,SUM($O$5:$O$304))</f>
       </c>
-      <c r="E21" s="164"/>
+      <c r="E21" s="156"/>
       <c r="G21" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -7877,15 +7877,15 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="143" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="171">
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="157">
         <f>COUNT($J$5:$J$304)</f>
       </c>
-      <c r="E23" s="148"/>
+      <c r="E23" s="140"/>
       <c r="G23" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -7918,15 +7918,15 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="143" t="s">
         <v>179</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="186">
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="167">
         <f>IFERROR($D$21*36500/($D$5*IF($D$8="FIJO",$D$7-$D$6,SUM($J$5:$J$304))),0)</f>
       </c>
-      <c r="E24" s="148"/>
+      <c r="E24" s="140"/>
       <c r="G24" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -15512,16 +15512,16 @@
     </row>
     <row r="261" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G261" s="11" t="str">
-        <f t="shared" ref="G261:G324" si="32">IF(H261="","",ROW()-4)</f>
+        <f t="shared" ref="G261:G304" si="32">IF(H261="","",ROW()-4)</f>
       </c>
       <c r="H261" s="12" t="str">
         <f t="shared" si="30"/>
       </c>
       <c r="I261" s="12" t="str">
-        <f t="shared" ref="I261:I324" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
+        <f t="shared" ref="I261:I304" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
       </c>
       <c r="J261" s="11" t="str">
-        <f t="shared" ref="J261:J324" si="34">IF(H261="","",I261-H261)</f>
+        <f t="shared" ref="J261:J304" si="34">IF(H261="","",I261-H261)</f>
       </c>
       <c r="K261" s="12" t="str">
         <f t="shared" si="31"/>
@@ -15533,10 +15533,10 @@
         <f t="shared" ref="M261:M304" si="35">IF(H261="","",IF($D$18="LEGAL",0,$D$10))</f>
       </c>
       <c r="N261" s="13" t="str">
-        <f t="shared" ref="N261:N324" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
+        <f t="shared" ref="N261:N304" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
       </c>
       <c r="O261" s="14" t="str">
-        <f t="shared" ref="O261:O324" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
+        <f t="shared" ref="O261:O304" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
       </c>
       <c r="P261" s="14" t="str">
         <f>IF(H261="","",$D$5+SUM($O$5:O261))</f>
@@ -16920,6 +16920,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D8:E8"/>
@@ -16934,30 +16956,8 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait"/>
@@ -16988,53 +16988,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="168" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="170" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="4" spans="1:16" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="152" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="140"/>
       <c r="G4" s="4" t="s">
         <v>163</v>
       </c>
@@ -17067,15 +17067,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="167">
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="159">
         <f>'Informe Subasta'!$D$10</f>
       </c>
-      <c r="E5" s="148"/>
+      <c r="E5" s="140"/>
       <c r="G5" s="11">
         <f t="shared" ref="G5:G68" si="0">IF(H5="","",ROW()-4)</f>
       </c>
@@ -17108,15 +17108,15 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="143" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="147"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="182">
+      <c r="B6" s="139"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="166">
         <f>'Informe Subasta'!$D$15</f>
       </c>
-      <c r="E6" s="148"/>
+      <c r="E6" s="140"/>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17149,15 +17149,15 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="147"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="182">
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="166">
         <f>'Informe Subasta'!$D$16</f>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="140"/>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17190,15 +17190,15 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="147"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="175" t="str">
+      <c r="B8" s="139"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="148" t="str">
         <f>'Informe Subasta'!$D$20</f>
       </c>
-      <c r="E8" s="148"/>
+      <c r="E8" s="140"/>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17231,15 +17231,15 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="175" t="str">
+      <c r="B9" s="139"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="148" t="str">
         <f>'Informe Subasta'!$K$20</f>
       </c>
-      <c r="E9" s="148"/>
+      <c r="E9" s="140"/>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17272,15 +17272,15 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="173">
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="153">
         <f>'Informe Subasta'!$K$21+3</f>
       </c>
-      <c r="E10" s="148"/>
+      <c r="E10" s="140"/>
       <c r="G10" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17313,15 +17313,15 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="143" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="175">
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="148">
         <f>'Informe Subasta'!$K$22</f>
       </c>
-      <c r="E11" s="148"/>
+      <c r="E11" s="140"/>
       <c r="G11" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17354,15 +17354,15 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="182">
+      <c r="B12" s="139"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="166">
         <f>'Informe Subasta'!$K$23</f>
       </c>
-      <c r="E12" s="148"/>
+      <c r="E12" s="140"/>
       <c r="G12" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17395,15 +17395,15 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="143" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="175">
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="148">
         <f>'Informe Subasta'!$K$24</f>
       </c>
-      <c r="E13" s="148"/>
+      <c r="E13" s="140"/>
       <c r="G13" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17436,15 +17436,15 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="175" t="str">
+      <c r="B14" s="139"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="148" t="str">
         <f>'Informe Subasta'!$D$24</f>
       </c>
-      <c r="E14" s="148"/>
+      <c r="E14" s="140"/>
       <c r="G14" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17477,15 +17477,15 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="143" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="175" t="str">
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="148" t="str">
         <f>'Informe Subasta'!$D$21</f>
       </c>
-      <c r="E15" s="148"/>
+      <c r="E15" s="140"/>
       <c r="G15" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17518,15 +17518,15 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="183">
+      <c r="B16" s="139"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="171">
         <f>'Informe Subasta'!$D$22</f>
       </c>
-      <c r="E16" s="148"/>
+      <c r="E16" s="140"/>
       <c r="G16" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17559,15 +17559,15 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="146" t="s">
+      <c r="A17" s="143" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="183">
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="171">
         <f>'Informe Subasta'!$D$23</f>
       </c>
-      <c r="E17" s="148"/>
+      <c r="E17" s="140"/>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17600,15 +17600,15 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="146" t="s">
+      <c r="A18" s="143" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="185" t="str">
+      <c r="B18" s="139"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="169" t="str">
         <f>IF(OR(ISNUMBER(SEARCH("legal",$D$9)),ISNUMBER(SEARCH("demora",$D$9)),ISNUMBER(SEARCH("mora procesal",$D$9)),ISNUMBER(SEARCH("576",$D$9))),"LEGAL","VARIABLE")</f>
       </c>
-      <c r="E18" s="148"/>
+      <c r="E18" s="140"/>
       <c r="G18" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17676,10 +17676,10 @@
       <c r="A20" s="152" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="148"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="140"/>
       <c r="G20" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17712,15 +17712,15 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="143" t="s">
         <v>177</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="181">
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="172">
         <f>IF($D$8="FIJO",($D$7-$D$6)*IF($D$15="Y",$D$16,$D$17)*$D$5/365,SUM($O$5:$O$304))</f>
       </c>
-      <c r="E21" s="164"/>
+      <c r="E21" s="156"/>
       <c r="G21" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -17787,15 +17787,15 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="143" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="171">
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="157">
         <f>COUNT($J$5:$J$304)</f>
       </c>
-      <c r="E23" s="148"/>
+      <c r="E23" s="140"/>
       <c r="G23" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -17828,15 +17828,15 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="143" t="s">
         <v>179</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="186">
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="167">
         <f>IFERROR($D$21*36500/($D$5*IF($D$8="FIJO",$D$7-$D$6,SUM($J$5:$J$304))),0)</f>
       </c>
-      <c r="E24" s="148"/>
+      <c r="E24" s="140"/>
       <c r="G24" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -25422,16 +25422,16 @@
     </row>
     <row r="261" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G261" s="11" t="str">
-        <f t="shared" ref="G261:G324" si="32">IF(H261="","",ROW()-4)</f>
+        <f t="shared" ref="G261:G304" si="32">IF(H261="","",ROW()-4)</f>
       </c>
       <c r="H261" s="12" t="str">
         <f t="shared" si="30"/>
       </c>
       <c r="I261" s="12" t="str">
-        <f t="shared" ref="I261:I324" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
+        <f t="shared" ref="I261:I304" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
       </c>
       <c r="J261" s="11" t="str">
-        <f t="shared" ref="J261:J324" si="34">IF(H261="","",I261-H261)</f>
+        <f t="shared" ref="J261:J304" si="34">IF(H261="","",I261-H261)</f>
       </c>
       <c r="K261" s="12" t="str">
         <f t="shared" si="31"/>
@@ -25443,10 +25443,10 @@
         <f t="shared" ref="M261:M304" si="35">IF(H261="","",IF($D$18="LEGAL",0,$D$10))</f>
       </c>
       <c r="N261" s="13" t="str">
-        <f t="shared" ref="N261:N324" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
+        <f t="shared" ref="N261:N304" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
       </c>
       <c r="O261" s="14" t="str">
-        <f t="shared" ref="O261:O324" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
+        <f t="shared" ref="O261:O304" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
       </c>
       <c r="P261" s="14" t="str">
         <f>IF(H261="","",$D$5+SUM($O$5:O261))</f>
@@ -26830,6 +26830,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D8:E8"/>
@@ -26844,30 +26866,8 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait"/>
@@ -27014,53 +27014,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="168" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="187" t="s">
+      <c r="A2" s="170" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="138"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="138"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="138"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
     </row>
     <row r="4" spans="1:16" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="152" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="148"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="140"/>
       <c r="G4" s="4" t="s">
         <v>163</v>
       </c>
@@ -27093,15 +27093,15 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="167">
+      <c r="B5" s="139"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="159">
         <f>'Informe Subasta'!$D$10</f>
       </c>
-      <c r="E5" s="148"/>
+      <c r="E5" s="140"/>
       <c r="G5" s="11">
         <f t="shared" ref="G5:G68" si="0">IF(H5="","",ROW()-4)</f>
       </c>
@@ -27134,15 +27134,15 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="143" t="s">
         <v>173</v>
       </c>
-      <c r="B6" s="147"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="182">
+      <c r="B6" s="139"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="166">
         <f>'Informe Subasta'!$D$15</f>
       </c>
-      <c r="E6" s="148"/>
+      <c r="E6" s="140"/>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27175,15 +27175,15 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="147"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="182">
+      <c r="B7" s="139"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="166">
         <f>'Informe Subasta'!$D$16</f>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="140"/>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27216,15 +27216,15 @@
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="147"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="175" t="str">
+      <c r="B8" s="139"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="148" t="str">
         <f>'Informe Subasta'!$D$20</f>
       </c>
-      <c r="E8" s="148"/>
+      <c r="E8" s="140"/>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27257,15 +27257,15 @@
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="147"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="175" t="str">
+      <c r="B9" s="139"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="148" t="str">
         <f>'Informe Subasta'!$K$20</f>
       </c>
-      <c r="E9" s="148"/>
+      <c r="E9" s="140"/>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27298,15 +27298,15 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="147"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="173">
+      <c r="B10" s="139"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="153">
         <f>'Informe Subasta'!$K$21</f>
       </c>
-      <c r="E10" s="148"/>
+      <c r="E10" s="140"/>
       <c r="G10" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27339,15 +27339,15 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="143" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="175">
+      <c r="B11" s="139"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="148">
         <f>'Informe Subasta'!$K$22</f>
       </c>
-      <c r="E11" s="148"/>
+      <c r="E11" s="140"/>
       <c r="G11" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27380,15 +27380,15 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="147"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="182">
+      <c r="B12" s="139"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="166">
         <f>'Informe Subasta'!$K$23</f>
       </c>
-      <c r="E12" s="148"/>
+      <c r="E12" s="140"/>
       <c r="G12" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27421,15 +27421,15 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="143" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="175">
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="148">
         <f>'Informe Subasta'!$K$24</f>
       </c>
-      <c r="E13" s="148"/>
+      <c r="E13" s="140"/>
       <c r="G13" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27462,15 +27462,15 @@
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="175" t="str">
+      <c r="B14" s="139"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="148" t="str">
         <f>'Informe Subasta'!$D$24</f>
       </c>
-      <c r="E14" s="148"/>
+      <c r="E14" s="140"/>
       <c r="G14" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27503,15 +27503,15 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="143" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="147"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="175" t="str">
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="148" t="str">
         <f>'Informe Subasta'!$D$21</f>
       </c>
-      <c r="E15" s="148"/>
+      <c r="E15" s="140"/>
       <c r="G15" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27544,15 +27544,15 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="183">
+      <c r="B16" s="139"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="171">
         <f>'Informe Subasta'!$D$22</f>
       </c>
-      <c r="E16" s="148"/>
+      <c r="E16" s="140"/>
       <c r="G16" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27585,15 +27585,15 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A17" s="146" t="s">
+      <c r="A17" s="143" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="183">
+      <c r="B17" s="139"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="171">
         <f>'Informe Subasta'!$D$23</f>
       </c>
-      <c r="E17" s="148"/>
+      <c r="E17" s="140"/>
       <c r="G17" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27626,15 +27626,15 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" s="146" t="s">
+      <c r="A18" s="143" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="185" t="str">
+      <c r="B18" s="139"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="169" t="str">
         <f>IF(OR(ISNUMBER(SEARCH("legal",$D$9)),ISNUMBER(SEARCH("demora",$D$9)),ISNUMBER(SEARCH("mora procesal",$D$9)),ISNUMBER(SEARCH("576",$D$9))),"LEGAL","VARIABLE")</f>
       </c>
-      <c r="E18" s="148"/>
+      <c r="E18" s="140"/>
       <c r="G18" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27702,10 +27702,10 @@
       <c r="A20" s="152" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="148"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="140"/>
       <c r="G20" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27738,15 +27738,15 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="143" t="s">
         <v>177</v>
       </c>
-      <c r="B21" s="147"/>
-      <c r="C21" s="148"/>
-      <c r="D21" s="181">
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="172">
         <f>IF($D$8="FIJO",($D$7-$D$6)*IF($D$15="Y",$D$16,$D$17)*$D$5/365,SUM($O$5:$O$304))</f>
       </c>
-      <c r="E21" s="164"/>
+      <c r="E21" s="156"/>
       <c r="G21" s="11">
         <f t="shared" si="0"/>
       </c>
@@ -27813,15 +27813,15 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="143" t="s">
         <v>178</v>
       </c>
-      <c r="B23" s="147"/>
-      <c r="C23" s="148"/>
-      <c r="D23" s="171">
+      <c r="B23" s="139"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="157">
         <f>COUNT($J$5:$J$304)</f>
       </c>
-      <c r="E23" s="148"/>
+      <c r="E23" s="140"/>
       <c r="G23" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -27854,15 +27854,15 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="146" t="s">
+      <c r="A24" s="143" t="s">
         <v>179</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="186">
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="167">
         <f>IFERROR($D$21*36500/($D$5*IF($D$8="FIJO",$D$7-$D$6,SUM($J$5:$J$304))),0)</f>
       </c>
-      <c r="E24" s="148"/>
+      <c r="E24" s="140"/>
       <c r="G24" s="11" t="str">
         <f t="shared" si="0"/>
       </c>
@@ -35448,16 +35448,16 @@
     </row>
     <row r="261" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G261" s="11" t="str">
-        <f t="shared" ref="G261:G324" si="32">IF(H261="","",ROW()-4)</f>
+        <f t="shared" ref="G261:G304" si="32">IF(H261="","",ROW()-4)</f>
       </c>
       <c r="H261" s="12" t="str">
         <f t="shared" si="30"/>
       </c>
       <c r="I261" s="12" t="str">
-        <f t="shared" ref="I261:I324" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
+        <f t="shared" ref="I261:I304" si="33">IF(H261="","",MIN(IF($D$18="LEGAL",DATE(YEAR(H261)+1,1,1),EDATE($D$12,$D$11*(INT((((YEAR(H261)-YEAR($D$12))*12+(MONTH(H261)-MONTH($D$12))-IF(DAY(H261)&lt;DAY($D$12),1,0))/$D$11))+1))),$D$7))</f>
       </c>
       <c r="J261" s="11" t="str">
-        <f t="shared" ref="J261:J324" si="34">IF(H261="","",I261-H261)</f>
+        <f t="shared" ref="J261:J304" si="34">IF(H261="","",I261-H261)</f>
       </c>
       <c r="K261" s="12" t="str">
         <f t="shared" si="31"/>
@@ -35469,10 +35469,10 @@
         <f t="shared" ref="M261:M304" si="35">IF(H261="","",IF($D$18="LEGAL",0,$D$10))</f>
       </c>
       <c r="N261" s="13" t="str">
-        <f t="shared" ref="N261:N324" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
+        <f t="shared" ref="N261:N304" si="36">IF(H261="","",IF(AND($D$14="Sí",(L261+M261)&lt;0),0,L261+M261))</f>
       </c>
       <c r="O261" s="14" t="str">
-        <f t="shared" ref="O261:O324" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
+        <f t="shared" ref="O261:O304" si="37">IF(H261="","",$D$5*N261*J261/36500)</f>
       </c>
       <c r="P261" s="14" t="str">
         <f>IF(H261="","",$D$5+SUM($O$5:O261))</f>
@@ -36856,6 +36856,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D8:E8"/>
@@ -36870,30 +36892,8 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D16:E16"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait"/>
@@ -36911,13 +36911,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="168" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="67" t="s">
@@ -36931,35 +36931,35 @@
       <c r="A3" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="173" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="170" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
     </row>
     <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="69" t="s">
@@ -47897,18 +47897,18 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="189" t="s">
+      <c r="B6" s="174" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="190"/>
-      <c r="D6" s="189" t="s">
+      <c r="C6" s="175"/>
+      <c r="D6" s="174" t="s">
         <v>207</v>
       </c>
-      <c r="E6" s="190"/>
-      <c r="F6" s="189" t="s">
+      <c r="E6" s="175"/>
+      <c r="F6" s="174" t="s">
         <v>208</v>
       </c>
-      <c r="G6" s="190"/>
+      <c r="G6" s="175"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="91" t="s">
@@ -48107,10 +48107,10 @@
       <c r="U17" s="20"/>
     </row>
     <row r="18" spans="2:21" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="194" t="s">
+      <c r="B18" s="179" t="s">
         <v>220</v>
       </c>
-      <c r="C18" s="190"/>
+      <c r="C18" s="175"/>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="20"/>
@@ -48133,30 +48133,30 @@
     <row r="19" spans="2:21" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
-      <c r="D19" s="193" t="s">
+      <c r="D19" s="178" t="s">
         <v>221</v>
       </c>
-      <c r="E19" s="192"/>
-      <c r="F19" s="192"/>
-      <c r="G19" s="192"/>
-      <c r="H19" s="190"/>
+      <c r="E19" s="177"/>
+      <c r="F19" s="177"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="175"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="191" t="s">
+      <c r="J19" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="K19" s="192"/>
-      <c r="L19" s="192"/>
-      <c r="M19" s="192"/>
-      <c r="N19" s="192"/>
-      <c r="O19" s="190"/>
-      <c r="P19" s="193" t="s">
+      <c r="K19" s="177"/>
+      <c r="L19" s="177"/>
+      <c r="M19" s="177"/>
+      <c r="N19" s="177"/>
+      <c r="O19" s="175"/>
+      <c r="P19" s="178" t="s">
         <v>223</v>
       </c>
-      <c r="Q19" s="192"/>
-      <c r="R19" s="192"/>
-      <c r="S19" s="192"/>
-      <c r="T19" s="192"/>
-      <c r="U19" s="190"/>
+      <c r="Q19" s="177"/>
+      <c r="R19" s="177"/>
+      <c r="S19" s="177"/>
+      <c r="T19" s="177"/>
+      <c r="U19" s="175"/>
     </row>
     <row r="20" spans="2:21" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="49" t="s">
@@ -50204,12 +50204,12 @@
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="N11" s="195" t="s">
+      <c r="N11" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="O11" s="147"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="148"/>
+      <c r="O11" s="139"/>
+      <c r="P11" s="139"/>
+      <c r="Q11" s="140"/>
     </row>
     <row r="12" spans="2:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="79" t="s">
@@ -51199,18 +51199,18 @@
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="130" t="s">
+      <c r="C6" s="183"/>
+      <c r="D6" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="131"/>
-      <c r="F6" s="130" t="s">
+      <c r="E6" s="183"/>
+      <c r="F6" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="131"/>
+      <c r="G6" s="183"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="22" t="s">
@@ -51261,19 +51261,19 @@
       <c r="C9" s="30">
         <f>'Informe Subasta'!$D$12</f>
       </c>
-      <c r="D9" s="134" t="s">
+      <c r="D9" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="136">
+      <c r="E9" s="195">
         <f>+$E$25</f>
       </c>
-      <c r="F9" s="143" t="s">
+      <c r="F9" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="132" t="e">
+      <c r="G9" s="191" t="e">
         <f>+$E$41</f>
       </c>
-      <c r="H9" s="137" t="s">
+      <c r="H9" s="181" t="s">
         <v>13</v>
       </c>
       <c r="I9" s="27"/>
@@ -51285,11 +51285,11 @@
       <c r="C10" s="32">
         <f>G17</f>
       </c>
-      <c r="D10" s="135"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="138"/>
+      <c r="D10" s="194"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="131"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B11" s="33" t="s">
@@ -51310,7 +51310,7 @@
       <c r="G11" s="34" t="e">
         <f>+$F$41</f>
       </c>
-      <c r="H11" s="138"/>
+      <c r="H11" s="131"/>
       <c r="I11" s="20"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
@@ -51355,17 +51355,17 @@
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B15" s="139" t="s">
+      <c r="B15" s="186" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="140"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="140"/>
-      <c r="I15" s="140"/>
-      <c r="J15" s="137" t="s">
+      <c r="C15" s="187"/>
+      <c r="D15" s="187"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="187"/>
+      <c r="H15" s="187"/>
+      <c r="I15" s="187"/>
+      <c r="J15" s="181" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="71" t="s">
@@ -51398,7 +51398,7 @@
       <c r="I16" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="138"/>
+      <c r="J16" s="131"/>
       <c r="S16" s="41"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
@@ -51426,19 +51426,19 @@
       <c r="I17" s="47">
         <f>+IF($H$17="Y",($C$7+$C$8+$C$9+$C$12)*0.05,0)</f>
       </c>
-      <c r="J17" s="138"/>
+      <c r="J17" s="131"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="B19" s="145" t="s">
+      <c r="B19" s="184" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="142"/>
-      <c r="I19" s="142"/>
+      <c r="C19" s="185"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="185"/>
+      <c r="G19" s="185"/>
+      <c r="H19" s="185"/>
+      <c r="I19" s="185"/>
     </row>
     <row r="20" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="48"/>
@@ -51602,15 +51602,15 @@
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="B27" s="141" t="s">
+      <c r="B27" s="188" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="142"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="142"/>
+      <c r="C27" s="185"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
       <c r="L27" s="27"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.35">
@@ -51753,15 +51753,15 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B35" s="141" t="s">
+      <c r="B35" s="188" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="142"/>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="142"/>
+      <c r="C35" s="185"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="185"/>
+      <c r="G35" s="185"/>
+      <c r="H35" s="185"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="49" t="s">
@@ -51903,11 +51903,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="B15:I15"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="B35:H35"/>
@@ -51916,6 +51911,11 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="B15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52220,6 +52220,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="17a21aa5-e6e0-4ea1-a8b7-dab22934b373" xsi:nil="true"/>
@@ -52228,15 +52237,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52475,6 +52475,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5271C44-2020-40E1-8747-2E1080B96F61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7149E0A2-98F7-41FE-BA20-FCBC9DF31DEE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -52485,14 +52493,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5271C44-2020-40E1-8747-2E1080B96F61}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AB1A57B-DF6F-4FA5-BFE6-92399F59170A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1a371a86-75ee-45af-9d35-73da47a1d8df"/>
+    <ds:schemaRef ds:uri="17a21aa5-e6e0-4ea1-a8b7-dab22934b373"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AB1A57B-DF6F-4FA5-BFE6-92399F59170A}"/>
 </file>